--- a/Data/FlightPlan/FPL_31OCT26.xlsx
+++ b/Data/FlightPlan/FPL_31OCT26.xlsx
@@ -125,6 +125,12 @@
     <t>14:20</t>
   </si>
   <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
     <t>17:35</t>
   </si>
   <si>
@@ -164,9 +170,6 @@
     <t>DLI</t>
   </si>
   <si>
-    <t>15:10</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -254,7 +257,7 @@
     <t>PUS</t>
   </si>
   <si>
-    <t>11:40</t>
+    <t>12:10</t>
   </si>
   <si>
     <t>12:40</t>
@@ -383,9 +386,6 @@
     <t>SIN</t>
   </si>
   <si>
-    <t>12:10</t>
-  </si>
-  <si>
     <t>15:15</t>
   </si>
   <si>
@@ -410,405 +410,405 @@
     <t>VN-A535</t>
   </si>
   <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
     <t>07:25</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
     <t>KHH</t>
   </si>
   <si>
@@ -1175,7 +1175,7 @@
     <t>Total Record(s): 352</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 30, 2026 22:12</t>
+    <t xml:space="preserve">Generated on  Oct 31, 2026 02:51</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1994,9 +1994,13 @@
       <c t="s" r="J15" s="7">
         <v>37</v>
       </c>
-      <c r="K15" s="7"/>
+      <c t="s" r="K15" s="7">
+        <v>38</v>
+      </c>
       <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
+      <c t="s" r="M15" s="7">
+        <v>39</v>
+      </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c t="s" r="A16" s="6">
@@ -2022,10 +2026,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I16" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c t="s" r="J16" s="7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -2055,10 +2059,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I17" s="7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c t="s" r="J17" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2091,7 +2095,7 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
@@ -2103,10 +2107,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2124,7 +2128,7 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
@@ -2136,10 +2140,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="D22" s="7"/>
       <c t="s" r="E22" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" s="7">
         <v>321</v>
@@ -2184,10 +2188,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2205,7 +2209,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2214,13 +2218,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2238,22 +2242,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H24" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
@@ -2280,13 +2284,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H25" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2319,22 +2323,22 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H27" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2352,7 +2356,7 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -2361,13 +2365,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2385,22 +2389,22 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2418,7 +2422,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2427,13 +2431,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2475,13 +2479,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2499,13 +2503,13 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>17</v>
@@ -2514,7 +2518,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2541,13 +2545,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H34" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2565,22 +2569,22 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2613,13 +2617,13 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>17</v>
@@ -2628,11 +2632,15 @@
         <v>26</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>81</v>
-      </c>
-      <c r="K37" s="7"/>
+        <v>38</v>
+      </c>
+      <c t="s" r="K37" s="7">
+        <v>33</v>
+      </c>
       <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
+      <c t="s" r="M37" s="7">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c t="s" r="A38" s="6">
@@ -2646,7 +2654,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2658,10 +2666,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2679,7 +2687,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2691,10 +2699,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2712,7 +2720,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2724,10 +2732,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2760,22 +2768,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2793,7 +2801,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2802,13 +2810,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2826,22 +2834,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2874,22 +2882,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2907,22 +2915,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2940,22 +2948,22 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2973,22 +2981,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3006,7 +3014,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3015,13 +3023,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3039,22 +3047,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3087,7 +3095,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3096,13 +3104,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3120,22 +3128,22 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3153,7 +3161,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3162,13 +3170,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3186,13 +3194,13 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>20</v>
@@ -3201,7 +3209,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3219,7 +3227,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3228,13 +3236,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3252,22 +3260,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3285,7 +3293,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3294,13 +3302,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3318,13 +3326,13 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>20</v>
@@ -3333,7 +3341,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3366,7 +3374,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3375,10 +3383,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>125</v>
@@ -3399,19 +3407,19 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>126</v>
@@ -3432,7 +3440,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3465,7 +3473,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3506,7 +3514,7 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>421</v>
+        <v>141</v>
       </c>
       <c t="s" r="C67" s="7">
         <v>14</v>
@@ -3522,7 +3530,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c t="s" r="I67" s="7">
         <v>133</v>
@@ -3539,7 +3547,7 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>422</v>
+        <v>148</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
@@ -3552,16 +3560,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3591,10 +3599,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3621,13 +3629,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H70" s="8">
+        <v>136</v>
+      </c>
+      <c t="s" r="I70" s="7">
         <v>137</v>
       </c>
-      <c t="s" r="I70" s="7">
+      <c t="s" r="J70" s="7">
         <v>138</v>
-      </c>
-      <c t="s" r="J70" s="7">
-        <v>139</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3651,16 +3659,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3687,13 +3695,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3717,16 +3725,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
+        <v>140</v>
+      </c>
+      <c t="s" r="H73" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I73" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="J73" s="7">
         <v>141</v>
-      </c>
-      <c t="s" r="H73" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I73" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>142</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3759,22 +3767,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
+        <v>142</v>
+      </c>
+      <c r="F75" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G75" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H75" s="8">
         <v>143</v>
       </c>
-      <c r="F75" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G75" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H75" s="8">
+      <c t="s" r="I75" s="7">
+        <v>107</v>
+      </c>
+      <c t="s" r="J75" s="7">
         <v>144</v>
-      </c>
-      <c t="s" r="I75" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>145</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3792,13 +3800,13 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
+        <v>142</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
         <v>143</v>
-      </c>
-      <c r="F76" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G76" s="8">
-        <v>144</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>17</v>
@@ -3807,7 +3815,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3825,7 +3833,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3840,7 +3848,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3870,10 +3878,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3891,22 +3899,22 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
+        <v>142</v>
+      </c>
+      <c r="F79" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G79" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H79" s="8">
         <v>143</v>
-      </c>
-      <c r="F79" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G79" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H79" s="8">
-        <v>144</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3924,22 +3932,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
+        <v>142</v>
+      </c>
+      <c r="F80" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G80" s="8">
         <v>143</v>
       </c>
-      <c r="F80" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G80" s="8">
-        <v>144</v>
-      </c>
       <c t="s" r="H80" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3957,7 +3965,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3969,7 +3977,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>149</v>
@@ -3990,7 +3998,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4086,7 +4094,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4149,7 +4157,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>160</v>
@@ -4230,7 +4238,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>165</v>
@@ -4260,13 +4268,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4290,13 +4298,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>167</v>
@@ -4326,13 +4334,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4356,7 +4364,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>20</v>
@@ -4440,7 +4448,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I97" s="7">
         <v>174</v>
@@ -4470,7 +4478,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>20</v>
@@ -4479,7 +4487,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4509,7 +4517,7 @@
         <v>178</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>159</v>
@@ -4587,13 +4595,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="I102" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J102" s="7">
         <v>181</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>182</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4617,13 +4625,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>174</v>
@@ -4653,13 +4661,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I104" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J104" s="7">
         <v>184</v>
-      </c>
-      <c t="s" r="J104" s="7">
-        <v>185</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4683,16 +4691,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4719,13 +4727,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4749,16 +4757,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
+        <v>186</v>
+      </c>
+      <c t="s" r="J107" s="7">
         <v>187</v>
-      </c>
-      <c t="s" r="J107" s="7">
-        <v>188</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4785,13 +4793,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4815,16 +4823,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
+        <v>189</v>
+      </c>
+      <c t="s" r="J109" s="7">
         <v>190</v>
-      </c>
-      <c t="s" r="J109" s="7">
-        <v>191</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4857,22 +4865,22 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
+        <v>191</v>
+      </c>
+      <c r="F111" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G111" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H111" s="8">
+        <v>71</v>
+      </c>
+      <c t="s" r="I111" s="7">
         <v>192</v>
       </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H111" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="I111" s="7">
-        <v>193</v>
-      </c>
       <c t="s" r="J111" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4890,22 +4898,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4923,7 +4931,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4932,10 +4940,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>26</v>
@@ -4971,22 +4979,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I115" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5004,22 +5012,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5037,19 +5045,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
+        <v>194</v>
+      </c>
+      <c r="F117" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G117" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H117" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I117" s="7">
         <v>195</v>
-      </c>
-      <c r="F117" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G117" s="8">
-        <v>55</v>
-      </c>
-      <c t="s" r="H117" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I117" s="7">
-        <v>196</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>158</v>
@@ -5085,13 +5093,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>162</v>
@@ -5100,7 +5108,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5118,7 +5126,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5127,13 +5135,13 @@
         <v>162</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5151,22 +5159,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5184,7 +5192,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5193,13 +5201,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I122" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J122" s="7">
         <v>199</v>
-      </c>
-      <c t="s" r="J122" s="7">
-        <v>200</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5217,19 +5225,19 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>150</v>
@@ -5250,7 +5258,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5259,13 +5267,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5298,7 +5306,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5313,7 +5321,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5331,7 +5339,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5343,10 +5351,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5364,22 +5372,22 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
+        <v>202</v>
+      </c>
+      <c r="F128" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G128" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H128" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I128" s="7">
         <v>203</v>
       </c>
-      <c r="F128" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G128" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H128" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="I128" s="7">
+      <c t="s" r="J128" s="7">
         <v>204</v>
-      </c>
-      <c t="s" r="J128" s="7">
-        <v>205</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5397,13 +5405,13 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
@@ -5412,7 +5420,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5430,7 +5438,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5442,10 +5450,10 @@
         <v>146</v>
       </c>
       <c t="s" r="I130" s="7">
+        <v>206</v>
+      </c>
+      <c t="s" r="J130" s="7">
         <v>207</v>
-      </c>
-      <c t="s" r="J130" s="7">
-        <v>208</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5463,7 +5471,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5475,10 +5483,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5496,7 +5504,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5508,7 +5516,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>25</v>
@@ -5544,22 +5552,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
+        <v>209</v>
+      </c>
+      <c r="F134" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G134" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H134" s="8">
+        <v>52</v>
+      </c>
+      <c t="s" r="I134" s="7">
         <v>210</v>
       </c>
-      <c r="F134" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G134" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H134" s="8">
-        <v>50</v>
-      </c>
-      <c t="s" r="I134" s="7">
-        <v>211</v>
-      </c>
       <c t="s" r="J134" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5577,22 +5585,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5610,22 +5618,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I136" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J136" s="7">
         <v>214</v>
-      </c>
-      <c t="s" r="J136" s="7">
-        <v>215</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5643,19 +5651,19 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>37</v>
@@ -5676,7 +5684,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5685,13 +5693,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5709,22 +5717,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5742,7 +5750,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5751,13 +5759,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5775,22 +5783,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5823,7 +5831,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5832,13 +5840,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5856,22 +5864,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
+        <v>219</v>
+      </c>
+      <c r="F144" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G144" s="8">
+        <v>113</v>
+      </c>
+      <c t="s" r="H144" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I144" s="7">
+        <v>62</v>
+      </c>
+      <c t="s" r="J144" s="7">
         <v>220</v>
-      </c>
-      <c r="F144" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G144" s="8">
-        <v>112</v>
-      </c>
-      <c t="s" r="H144" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I144" s="7">
-        <v>61</v>
-      </c>
-      <c t="s" r="J144" s="7">
-        <v>221</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5889,7 +5897,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5898,13 +5906,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5922,22 +5930,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5970,7 +5978,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5985,7 +5993,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6003,7 +6011,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6018,7 +6026,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6036,7 +6044,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6045,13 +6053,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>126</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6069,22 +6077,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
+        <v>226</v>
+      </c>
+      <c t="s" r="J151" s="7">
         <v>227</v>
-      </c>
-      <c t="s" r="J151" s="7">
-        <v>228</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6117,22 +6125,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
+        <v>228</v>
+      </c>
+      <c r="F153" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G153" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H153" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I153" s="7">
         <v>229</v>
       </c>
-      <c r="F153" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G153" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H153" s="8">
-        <v>55</v>
-      </c>
-      <c t="s" r="I153" s="7">
-        <v>230</v>
-      </c>
       <c t="s" r="J153" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6150,22 +6158,22 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
+        <v>230</v>
+      </c>
+      <c t="s" r="J154" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="J154" s="7">
-        <v>232</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6183,7 +6191,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6198,7 +6206,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6216,7 +6224,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6228,10 +6236,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6249,7 +6257,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6261,10 +6269,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6297,7 +6305,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6306,13 +6314,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6330,19 +6338,19 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
+        <v>233</v>
+      </c>
+      <c r="F160" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G160" s="8">
+        <v>211</v>
+      </c>
+      <c t="s" r="H160" s="8">
+        <v>143</v>
+      </c>
+      <c t="s" r="I160" s="7">
         <v>234</v>
-      </c>
-      <c r="F160" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G160" s="8">
-        <v>212</v>
-      </c>
-      <c t="s" r="H160" s="8">
-        <v>144</v>
-      </c>
-      <c t="s" r="I160" s="7">
-        <v>135</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>235</v>
@@ -6363,22 +6371,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>236</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6396,13 +6404,13 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>17</v>
@@ -6429,7 +6437,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6438,13 +6446,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>238</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6462,19 +6470,19 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>159</v>
@@ -6519,7 +6527,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>240</v>
@@ -6549,13 +6557,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>177</v>
@@ -6582,16 +6590,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6615,7 +6623,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>17</v>
@@ -6651,13 +6659,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6681,13 +6689,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>150</v>
@@ -6771,7 +6779,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6804,7 +6812,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6834,7 +6842,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>247</v>
@@ -6876,7 +6884,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>20</v>
@@ -6885,7 +6893,7 @@
         <v>249</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6948,10 +6956,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6978,10 +6986,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>252</v>
@@ -7008,13 +7016,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>21</v>
@@ -7047,7 +7055,7 @@
         <v>253</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>254</v>
@@ -7122,16 +7130,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7158,7 +7166,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>174</v>
@@ -7188,7 +7196,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>17</v>
@@ -7197,7 +7205,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7224,10 +7232,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>259</v>
@@ -7254,7 +7262,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>17</v>
@@ -7293,7 +7301,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>150</v>
@@ -7338,13 +7346,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>261</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7368,13 +7376,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>262</v>
@@ -7437,13 +7445,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7467,13 +7475,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>168</v>
@@ -7506,10 +7514,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7539,10 +7547,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7568,7 +7576,7 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>141</v>
+        <v>421</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
@@ -7584,13 +7592,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>265</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7601,7 +7609,7 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>148</v>
+        <v>422</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
@@ -7614,16 +7622,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7686,7 +7694,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>238</v>
@@ -7719,10 +7727,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7830,13 +7838,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7860,13 +7868,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>174</v>
@@ -7899,10 +7907,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7935,7 +7943,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7998,7 +8006,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>275</v>
@@ -8046,7 +8054,7 @@
         <v>242</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>174</v>
@@ -8109,10 +8117,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>237</v>
@@ -8139,16 +8147,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8214,7 +8222,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8253,16 +8261,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8286,7 +8294,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>279</v>
@@ -8322,13 +8330,13 @@
         <v>279</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8352,13 +8360,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>268</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>281</v>
@@ -8388,7 +8396,7 @@
         <v>268</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>179</v>
@@ -8439,10 +8447,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8502,13 +8510,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8532,16 +8540,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8583,7 +8591,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>286</v>
@@ -8613,7 +8621,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>17</v>
@@ -8685,10 +8693,10 @@
         <v>288</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8769,7 +8777,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8802,7 +8810,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8829,10 +8837,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>125</v>
@@ -8859,7 +8867,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>162</v>
@@ -8895,10 +8903,10 @@
         <v>162</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>291</v>
@@ -8943,10 +8951,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>174</v>
@@ -8973,16 +8981,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9015,7 +9023,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9042,7 +9050,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>148</v>
@@ -9072,13 +9080,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>247</v>
@@ -9126,7 +9134,7 @@
         <v>266</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>267</v>
@@ -9159,7 +9167,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>155</v>
@@ -9189,13 +9197,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>294</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9219,13 +9227,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>277</v>
@@ -9252,16 +9260,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9285,10 +9293,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>295</v>
@@ -9333,16 +9341,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9372,7 +9380,7 @@
         <v>297</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>238</v>
@@ -9405,7 +9413,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>298</v>
@@ -9489,7 +9497,7 @@
         <v>301</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9519,7 +9527,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>173</v>
@@ -9549,7 +9557,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>302</v>
@@ -9579,16 +9587,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9621,7 +9629,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9702,7 +9710,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9735,7 +9743,7 @@
         <v>267</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9762,10 +9770,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>309</v>
@@ -9792,16 +9800,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9828,10 +9836,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>310</v>
@@ -9858,7 +9866,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>17</v>
@@ -9909,10 +9917,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>240</v>
@@ -9939,7 +9947,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>20</v>
@@ -9948,7 +9956,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9975,7 +9983,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>243</v>
@@ -10005,7 +10013,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>20</v>
@@ -10014,7 +10022,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10044,7 +10052,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>126</v>
@@ -10077,10 +10085,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10110,7 +10118,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>315</v>
@@ -10152,13 +10160,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>235</v>
@@ -10188,13 +10196,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10218,7 +10226,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>17</v>
@@ -10227,7 +10235,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10254,13 +10262,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10284,7 +10292,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10293,7 +10301,7 @@
         <v>317</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10323,7 +10331,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>295</v>
@@ -10398,7 +10406,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>20</v>
@@ -10434,10 +10442,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>164</v>
@@ -10464,13 +10472,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>147</v>
@@ -10500,13 +10508,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>263</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10530,13 +10538,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>322</v>
@@ -10569,10 +10577,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10683,10 +10691,10 @@
         <v>327</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10716,10 +10724,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10746,10 +10754,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>328</v>
@@ -10776,7 +10784,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>20</v>
@@ -10785,7 +10793,7 @@
         <v>329</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10812,13 +10820,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10896,10 +10904,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10926,7 +10934,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>165</v>
@@ -10956,16 +10964,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10995,10 +11003,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11031,7 +11039,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11079,7 +11087,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11109,7 +11117,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>259</v>
@@ -11142,7 +11150,7 @@
         <v>334</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>335</v>
@@ -11223,7 +11231,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>166</v>
@@ -11256,10 +11264,10 @@
         <v>339</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11289,7 +11297,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>252</v>
@@ -11322,7 +11330,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>340</v>
@@ -11352,13 +11360,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11403,7 +11411,7 @@
         <v>342</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>166</v>
@@ -11439,7 +11447,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11472,7 +11480,7 @@
         <v>270</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11517,7 +11525,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>249</v>
@@ -11553,10 +11561,10 @@
         <v>301</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="K332" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
@@ -11617,7 +11625,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>19</v>
@@ -11647,7 +11655,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>20</v>
@@ -11656,7 +11664,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11683,13 +11691,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11713,7 +11721,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>20</v>
@@ -11722,7 +11730,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11797,13 +11805,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>333</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11827,7 +11835,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>20</v>
@@ -11836,7 +11844,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11863,7 +11871,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>348</v>
@@ -11893,7 +11901,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>20</v>
@@ -11902,7 +11910,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11947,10 +11955,10 @@
         <v>331</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11983,7 +11991,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12049,7 +12057,7 @@
         <v>350</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12079,10 +12087,10 @@
         <v>331</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12112,10 +12120,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I350" s="7">
+        <v>186</v>
+      </c>
+      <c t="s" r="J350" s="7">
         <v>187</v>
-      </c>
-      <c t="s" r="J350" s="7">
-        <v>188</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12145,7 +12153,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>21</v>
@@ -12181,7 +12189,7 @@
         <v>340</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12223,13 +12231,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>286</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12253,7 +12261,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>17</v>
@@ -12262,7 +12270,7 @@
         <v>352</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12289,7 +12297,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>353</v>
@@ -12319,13 +12327,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>177</v>
@@ -12358,10 +12366,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12391,7 +12399,7 @@
         <v>304</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>21</v>
@@ -12466,7 +12474,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>20</v>
@@ -12502,13 +12510,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>302</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12532,16 +12540,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12565,10 +12573,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>284</v>
@@ -12613,13 +12621,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>262</v>
@@ -12646,7 +12654,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>357</v>
@@ -12682,10 +12690,10 @@
         <v>357</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>129</v>
@@ -12712,16 +12720,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12763,13 +12771,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>359</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12793,16 +12801,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>235</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12826,13 +12834,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>155</v>
@@ -12859,7 +12867,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>35</v>
@@ -12913,7 +12921,7 @@
         <v>361</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>263</v>
@@ -12946,10 +12954,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12979,10 +12987,10 @@
         <v>331</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13012,10 +13020,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13090,13 +13098,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13120,13 +13128,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>165</v>
@@ -13156,7 +13164,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>250</v>
@@ -13186,16 +13194,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>279</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13222,13 +13230,13 @@
         <v>279</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13306,7 +13314,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>166</v>
@@ -13339,10 +13347,10 @@
         <v>300</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13405,7 +13413,7 @@
         <v>253</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>319</v>
@@ -13438,7 +13446,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>364</v>
@@ -13480,7 +13488,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>361</v>
@@ -13489,7 +13497,7 @@
         <v>352</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13516,10 +13524,10 @@
         <v>361</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>31</v>
@@ -13546,7 +13554,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>35</v>
@@ -13582,13 +13590,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>324</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13627,16 +13635,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>367</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13663,13 +13671,13 @@
         <v>367</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>315</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13750,7 +13758,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13783,7 +13791,7 @@
         <v>322</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13813,7 +13821,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>369</v>
@@ -13888,13 +13896,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>353</v>
@@ -13924,13 +13932,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13954,16 +13962,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>371</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13990,7 +13998,7 @@
         <v>371</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>372</v>
@@ -14035,13 +14043,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>374</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>21</v>
@@ -14071,7 +14079,7 @@
         <v>374</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>375</v>
@@ -14125,14 +14133,14 @@
         <v>301</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="K418" s="7">
         <v>377</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14162,14 +14170,14 @@
         <v>308</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c t="s" r="K419" s="7">
         <v>353</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14196,7 +14204,7 @@
         <v>379</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>348</v>
@@ -14229,7 +14237,7 @@
         <v>378</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>240</v>
@@ -14271,7 +14279,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>17</v>
@@ -14343,7 +14351,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>383</v>

--- a/Data/FlightPlan/FPL_31OCT26.xlsx
+++ b/Data/FlightPlan/FPL_31OCT26.xlsx
@@ -482,6 +482,9 @@
     <t>10:40</t>
   </si>
   <si>
+    <t>12:38</t>
+  </si>
+  <si>
     <t>15:55</t>
   </si>
   <si>
@@ -563,7 +566,7 @@
     <t>12:20</t>
   </si>
   <si>
-    <t>12:21</t>
+    <t>12:15</t>
   </si>
   <si>
     <t>C</t>
@@ -611,6 +614,9 @@
     <t>10:20</t>
   </si>
   <si>
+    <t>16:53</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
     <t>11:50</t>
   </si>
   <si>
+    <t>12:08</t>
+  </si>
+  <si>
     <t>13:45</t>
   </si>
   <si>
@@ -650,6 +659,9 @@
     <t>VN-A554</t>
   </si>
   <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>14:10</t>
   </si>
   <si>
@@ -707,7 +719,7 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>12:07</t>
+    <t>11:53</t>
   </si>
   <si>
     <t>12:30</t>
@@ -737,6 +749,9 @@
     <t>12:50</t>
   </si>
   <si>
+    <t>12:41</t>
+  </si>
+  <si>
     <t>HND</t>
   </si>
   <si>
@@ -824,9 +839,6 @@
     <t>11:36</t>
   </si>
   <si>
-    <t>12:15</t>
-  </si>
-  <si>
     <t>14:05</t>
   </si>
   <si>
@@ -896,6 +908,9 @@
     <t>10:34</t>
   </si>
   <si>
+    <t>13:12</t>
+  </si>
+  <si>
     <t>19:30</t>
   </si>
   <si>
@@ -908,333 +923,348 @@
     <t>10:46</t>
   </si>
   <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>11:43</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>WUX</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
     <t>12:27</t>
   </si>
   <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>03:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>12:09</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>08:39</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>11:43</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>10:43</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>11:13</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>WUX</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
     <t>VN-A685</t>
   </si>
   <si>
@@ -1256,6 +1286,9 @@
     <t>10:19</t>
   </si>
   <si>
+    <t>12:19</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1322,7 +1355,10 @@
     <t>PRG</t>
   </si>
   <si>
-    <t>00:20</t>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>02:10</t>
   </si>
   <si>
     <t>P</t>
@@ -1352,7 +1388,7 @@
     <t>Total Record(s): 352</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 31, 2026 10:34</t>
+    <t xml:space="preserve">Generated on  Oct 31, 2026 11:28</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4026,7 +4062,9 @@
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
+      <c t="s" r="M76" s="7">
+        <v>157</v>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c t="s" r="A77" s="6">
@@ -4085,10 +4123,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4121,7 +4159,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4151,10 +4189,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4187,7 +4225,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4220,7 +4258,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4232,7 +4270,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>78</v>
@@ -4253,7 +4291,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4265,7 +4303,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>32</v>
@@ -4286,7 +4324,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4298,10 +4336,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4334,7 +4372,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4343,18 +4381,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4369,13 +4407,13 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>27</v>
@@ -4384,12 +4422,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4404,7 +4442,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4416,7 +4454,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>46</v>
@@ -4437,7 +4475,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4449,7 +4487,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>68</v>
@@ -4470,7 +4508,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4482,7 +4520,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>41</v>
@@ -4503,7 +4541,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4515,10 +4553,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4551,7 +4589,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4563,10 +4601,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4586,7 +4624,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4598,15 +4636,15 @@
         <v>118</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4617,11 +4655,11 @@
         <v>6860</v>
       </c>
       <c t="s" r="C96" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4633,10 +4671,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4650,11 +4688,11 @@
         <v>6860</v>
       </c>
       <c t="s" r="C97" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4663,7 +4701,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="I97" s="7">
         <v>95</v>
@@ -4683,23 +4721,23 @@
         <v>6849</v>
       </c>
       <c t="s" r="C98" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>33</v>
@@ -4735,7 +4773,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4750,12 +4788,12 @@
         <v>138</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4770,7 +4808,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4782,15 +4820,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4805,7 +4843,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4817,10 +4855,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4838,7 +4876,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4871,7 +4909,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4883,7 +4921,7 @@
         <v>150</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>56</v>
@@ -4904,7 +4942,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4919,7 +4957,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4937,7 +4975,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4952,7 +4990,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4970,7 +5008,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5018,7 +5056,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5030,14 +5068,16 @@
         <v>74</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
+      <c t="s" r="M109" s="7">
+        <v>201</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c t="s" r="A110" s="6">
@@ -5051,7 +5091,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5066,7 +5106,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5084,7 +5124,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5096,7 +5136,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>43</v>
@@ -5132,7 +5172,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5144,15 +5184,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5167,7 +5207,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5179,14 +5219,16 @@
         <v>59</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
+      <c t="s" r="M114" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c t="s" r="A115" s="6">
@@ -5200,7 +5242,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5212,10 +5254,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5233,7 +5275,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5242,13 +5284,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5266,22 +5308,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5314,7 +5356,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5323,7 +5365,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>156</v>
@@ -5333,7 +5375,9 @@
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
+      <c t="s" r="M119" s="7">
+        <v>216</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c t="s" r="A120" s="6">
@@ -5347,13 +5391,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>59</v>
@@ -5362,7 +5406,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5380,7 +5424,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5392,10 +5436,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5413,7 +5457,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5425,10 +5469,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5446,7 +5490,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5458,7 +5502,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>147</v>
@@ -5479,7 +5523,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5491,7 +5535,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>134</v>
@@ -5527,7 +5571,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5539,15 +5583,15 @@
         <v>155</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5562,7 +5606,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5574,7 +5618,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>102</v>
@@ -5582,7 +5626,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5597,7 +5641,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5609,10 +5653,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5630,7 +5674,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5645,7 +5689,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5663,7 +5707,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5675,10 +5719,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5696,7 +5740,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5729,7 +5773,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5744,7 +5788,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5777,7 +5821,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5789,15 +5833,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5812,7 +5856,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5821,18 +5865,18 @@
         <v>54</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5847,27 +5891,27 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -5882,7 +5926,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5894,7 +5938,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>37</v>
@@ -5915,7 +5959,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5930,7 +5974,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5948,7 +5992,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5960,10 +6004,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5981,7 +6025,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6014,7 +6058,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6026,10 +6070,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6058,11 +6102,11 @@
         <v>6869</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6082,7 +6126,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6097,7 +6141,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6112,7 +6156,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6130,7 +6174,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6145,7 +6189,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6163,7 +6207,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6175,7 +6219,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>60</v>
@@ -6211,7 +6255,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6226,11 +6270,13 @@
         <v>156</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>246</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
@@ -6244,7 +6290,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6256,7 +6302,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>48</v>
@@ -6277,7 +6323,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6286,13 +6332,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6310,22 +6356,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6358,7 +6404,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6378,7 +6424,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6393,7 +6439,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6405,15 +6451,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6428,7 +6474,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6437,13 +6483,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6461,19 +6507,19 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>48</v>
@@ -6494,7 +6540,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6506,7 +6552,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>89</v>
@@ -6542,7 +6588,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6551,7 +6597,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>138</v>
@@ -6577,27 +6623,27 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>150</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6612,7 +6658,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6621,13 +6667,13 @@
         <v>150</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6645,13 +6691,13 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>17</v>
@@ -6660,7 +6706,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6678,7 +6724,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6690,10 +6736,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6711,7 +6757,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6723,7 +6769,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>133</v>
@@ -6759,7 +6805,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6779,7 +6825,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6794,7 +6840,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6809,7 +6855,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6827,7 +6873,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6860,7 +6906,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6872,10 +6918,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6893,7 +6939,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6905,7 +6951,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>86</v>
@@ -6926,7 +6972,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6974,7 +7020,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6983,18 +7029,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7009,19 +7055,19 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>46</v>
@@ -7042,7 +7088,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7051,13 +7097,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7075,22 +7121,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7123,7 +7169,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7135,15 +7181,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7158,7 +7204,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7167,13 +7213,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7191,19 +7237,19 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>56</v>
@@ -7224,7 +7270,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7236,10 +7282,10 @@
         <v>118</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7257,7 +7303,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7290,7 +7336,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7302,10 +7348,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7338,7 +7384,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7350,7 +7396,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>75</v>
@@ -7358,7 +7404,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7373,7 +7419,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7385,15 +7431,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7408,7 +7454,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7420,10 +7466,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7441,7 +7487,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7456,7 +7502,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7474,7 +7520,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7489,7 +7535,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7507,7 +7553,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7519,7 +7565,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>88</v>
@@ -7540,7 +7586,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7555,7 +7601,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7588,7 +7634,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7600,7 +7646,7 @@
         <v>120</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>153</v>
@@ -7608,7 +7654,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7623,7 +7669,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7635,7 +7681,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>102</v>
@@ -7643,7 +7689,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7658,7 +7704,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7667,10 +7713,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>129</v>
@@ -7691,13 +7737,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>27</v>
@@ -7706,7 +7752,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7724,7 +7770,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7736,7 +7782,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>89</v>
@@ -7757,7 +7803,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7766,13 +7812,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7790,22 +7836,22 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7838,7 +7884,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7858,7 +7904,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -7873,7 +7919,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7885,15 +7931,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7908,7 +7954,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7920,14 +7966,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>87</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>299</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
@@ -7941,7 +7989,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7974,7 +8022,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7983,13 +8031,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8007,13 +8055,13 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>27</v>
@@ -8022,7 +8070,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8055,7 +8103,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8064,18 +8112,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="I208" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8090,27 +8138,27 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8125,7 +8173,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8134,10 +8182,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>145</v>
@@ -8158,22 +8206,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8191,7 +8239,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8203,7 +8251,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>108</v>
@@ -8224,7 +8272,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8236,10 +8284,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8272,7 +8320,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8287,12 +8335,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8307,7 +8355,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8316,13 +8364,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8340,13 +8388,13 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>59</v>
@@ -8369,11 +8417,11 @@
         <v>5840</v>
       </c>
       <c t="s" r="C218" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8382,13 +8430,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8402,26 +8450,26 @@
         <v>5841</v>
       </c>
       <c t="s" r="C219" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8454,7 +8502,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8469,7 +8517,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8489,7 +8537,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8522,7 +8570,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8531,13 +8579,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8555,22 +8603,22 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8603,7 +8651,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8615,7 +8663,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>18</v>
@@ -8623,7 +8671,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8638,7 +8686,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8650,15 +8698,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8673,7 +8721,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8682,13 +8730,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8706,19 +8754,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>40</v>
@@ -8739,7 +8787,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8751,7 +8799,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>101</v>
@@ -8787,7 +8835,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8799,15 +8847,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8822,7 +8870,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8834,15 +8882,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8857,7 +8905,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8869,7 +8917,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>46</v>
@@ -8890,7 +8938,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8899,7 +8947,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>55</v>
@@ -8923,13 +8971,13 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>27</v>
@@ -8956,7 +9004,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8971,7 +9019,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8989,7 +9037,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9001,7 +9049,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>42</v>
@@ -9037,7 +9085,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9049,15 +9097,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9072,7 +9120,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9091,7 +9139,9 @@
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
-      <c r="M241" s="7"/>
+      <c t="s" r="M241" s="7">
+        <v>331</v>
+      </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
@@ -9105,7 +9155,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9117,7 +9167,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>48</v>
@@ -9138,7 +9188,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9150,10 +9200,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9171,7 +9221,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9183,10 +9233,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9204,7 +9254,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9213,13 +9263,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9237,22 +9287,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9285,7 +9335,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9294,18 +9344,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9320,26 +9370,28 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
-      <c r="M249" s="7"/>
+      <c t="s" r="M249" s="7">
+        <v>176</v>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c t="s" r="A250" s="6">
@@ -9353,7 +9405,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9365,7 +9417,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>121</v>
@@ -9386,7 +9438,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9401,7 +9453,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9419,7 +9471,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9452,7 +9504,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9464,10 +9516,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9500,7 +9552,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9512,10 +9564,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9535,7 +9587,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9544,13 +9596,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>145</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9568,13 +9620,13 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>27</v>
@@ -9583,7 +9635,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9601,7 +9653,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9613,10 +9665,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9649,7 +9701,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9658,18 +9710,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9684,27 +9736,27 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9719,7 +9771,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -9728,18 +9780,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -9754,13 +9806,13 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
@@ -9769,7 +9821,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9787,7 +9839,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9796,10 +9848,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>109</v>
@@ -9820,22 +9872,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9868,7 +9920,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9877,10 +9929,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>117</v>
@@ -9888,7 +9940,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -9903,19 +9955,19 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>87</v>
@@ -9936,7 +9988,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9948,10 +10000,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9969,7 +10021,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9978,10 +10030,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>125</v>
@@ -10002,22 +10054,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10050,7 +10102,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10062,7 +10114,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>139</v>
@@ -10070,7 +10122,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10085,7 +10137,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10097,7 +10149,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>153</v>
@@ -10105,7 +10157,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10120,7 +10172,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10132,14 +10184,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>85</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
-      <c r="M275" s="7"/>
+      <c t="s" r="M275" s="7">
+        <v>359</v>
+      </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
@@ -10153,7 +10207,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10186,7 +10240,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10195,13 +10249,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10219,13 +10273,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>94</v>
@@ -10234,7 +10288,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10252,7 +10306,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10300,7 +10354,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10315,7 +10369,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10333,7 +10387,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10345,10 +10399,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10366,7 +10420,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10378,7 +10432,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>132</v>
@@ -10399,7 +10453,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10447,7 +10501,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10462,12 +10516,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10482,7 +10536,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10497,7 +10551,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10515,7 +10569,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10527,7 +10581,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>46</v>
@@ -10548,7 +10602,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10581,7 +10635,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10593,7 +10647,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>121</v>
@@ -10614,7 +10668,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10662,7 +10716,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10677,12 +10731,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10697,7 +10751,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10712,12 +10766,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10732,7 +10786,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10767,7 +10821,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10779,14 +10833,16 @@
         <v>59</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
-      <c r="M296" s="7"/>
+      <c t="s" r="M296" s="7">
+        <v>369</v>
+      </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
       <c t="s" r="A297" s="6">
@@ -10800,7 +10856,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10812,10 +10868,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10833,7 +10889,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10848,7 +10904,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10866,7 +10922,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10881,7 +10937,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10899,7 +10955,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10908,13 +10964,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10932,22 +10988,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10980,7 +11036,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10989,18 +11045,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="I303" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11015,22 +11071,22 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11048,7 +11104,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11063,7 +11119,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11081,7 +11137,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11093,10 +11149,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11114,7 +11170,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11123,10 +11179,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>115</v>
@@ -11162,7 +11218,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11171,18 +11227,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11197,13 +11253,13 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>27</v>
@@ -11212,12 +11268,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11232,7 +11288,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11244,10 +11300,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11265,7 +11321,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11298,7 +11354,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11307,13 +11363,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11331,19 +11387,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>89</v>
@@ -11379,7 +11435,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11388,18 +11444,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11414,13 +11470,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
@@ -11429,7 +11485,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11447,7 +11503,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11456,13 +11512,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11480,22 +11536,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11528,13 +11584,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>27</v>
@@ -11543,12 +11599,12 @@
         <v>64</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11563,7 +11619,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11572,7 +11628,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>77</v>
@@ -11596,22 +11652,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11644,7 +11700,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11653,18 +11709,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>111</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -11679,19 +11735,19 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>96</v>
@@ -11712,7 +11768,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11721,13 +11777,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11760,7 +11816,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11772,15 +11828,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11795,7 +11851,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11807,17 +11863,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>75</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11832,7 +11888,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11844,7 +11900,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>29</v>
@@ -11865,7 +11921,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11880,7 +11936,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11898,7 +11954,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11910,7 +11966,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>78</v>
@@ -11931,7 +11987,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11943,7 +11999,7 @@
         <v>150</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>41</v>
@@ -11964,7 +12020,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11976,7 +12032,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>109</v>
@@ -11997,7 +12053,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12009,7 +12065,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>115</v>
@@ -12045,7 +12101,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12057,7 +12113,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>65</v>
@@ -12065,7 +12121,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12080,7 +12136,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12092,7 +12148,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>78</v>
@@ -12113,7 +12169,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12125,7 +12181,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>148</v>
@@ -12146,7 +12202,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12158,7 +12214,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>82</v>
@@ -12194,7 +12250,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12203,7 +12259,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>151</v>
@@ -12214,7 +12270,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12229,27 +12285,27 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12264,7 +12320,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12273,17 +12329,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
@@ -12297,22 +12355,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12330,7 +12388,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12339,7 +12397,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>145</v>
@@ -12363,22 +12421,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12396,7 +12454,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12408,7 +12466,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>125</v>
@@ -12429,7 +12487,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12441,10 +12499,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12477,7 +12535,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12489,15 +12547,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12512,7 +12570,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12521,20 +12579,20 @@
         <v>100</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="K353" s="7">
         <v>28</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>67</v>
+        <v>409</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12549,19 +12607,19 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>31</v>
@@ -12571,7 +12629,7 @@
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12586,7 +12644,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12598,17 +12656,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="K355" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12623,7 +12681,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12632,13 +12690,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12656,22 +12714,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12704,7 +12762,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12719,12 +12777,12 @@
         <v>115</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12739,7 +12797,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12751,7 +12809,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>102</v>
@@ -12759,7 +12817,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12774,7 +12832,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12807,7 +12865,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12822,7 +12880,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12840,7 +12898,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12855,7 +12913,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12888,7 +12946,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12903,7 +12961,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12923,7 +12981,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12932,13 +12990,13 @@
         <v>118</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12956,13 +13014,13 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>118</v>
@@ -12989,7 +13047,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13037,7 +13095,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13049,15 +13107,15 @@
         <v>118</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13072,7 +13130,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13084,14 +13142,16 @@
         <v>94</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>85</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>417</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -13105,7 +13165,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13120,7 +13180,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13138,7 +13198,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13150,7 +13210,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>72</v>
@@ -13186,7 +13246,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13195,18 +13255,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>101</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13221,13 +13281,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>27</v>
@@ -13236,7 +13296,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13254,7 +13314,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13263,13 +13323,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c t="s" r="I377" s="7">
         <v>145</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13287,22 +13347,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13320,7 +13380,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13332,7 +13392,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>24</v>
@@ -13368,7 +13428,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13380,7 +13440,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>153</v>
@@ -13388,7 +13448,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13403,7 +13463,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13415,10 +13475,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13438,7 +13498,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13450,10 +13510,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13471,7 +13531,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13480,13 +13540,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13504,22 +13564,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13552,7 +13612,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13561,18 +13621,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13587,13 +13647,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
@@ -13602,11 +13662,13 @@
         <v>102</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
-      <c r="M388" s="7"/>
+      <c t="s" r="M388" s="7">
+        <v>425</v>
+      </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
       <c t="s" r="A389" s="6">
@@ -13620,7 +13682,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13629,10 +13691,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>48</v>
@@ -13653,19 +13715,19 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>130</v>
@@ -13686,7 +13748,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13698,10 +13760,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13719,7 +13781,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13728,13 +13790,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13752,22 +13814,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13800,7 +13862,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13812,10 +13874,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13835,7 +13897,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13847,17 +13909,17 @@
         <v>142</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13872,7 +13934,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13887,14 +13949,14 @@
         <v>105</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="K397" s="7">
         <v>65</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -13909,7 +13971,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13918,10 +13980,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>148</v>
@@ -13942,22 +14004,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13990,7 +14052,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13999,10 +14061,10 @@
         <v>118</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>108</v>
@@ -14023,19 +14085,19 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>118</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>116</v>
@@ -14071,7 +14133,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14083,15 +14145,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14106,7 +14168,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14118,10 +14180,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14139,7 +14201,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14151,7 +14213,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>146</v>
@@ -14172,7 +14234,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14184,10 +14246,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14205,7 +14267,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14253,7 +14315,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -14268,12 +14330,12 @@
         <v>153</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>426</v>
+        <v>437</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14288,7 +14350,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14303,7 +14365,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14317,11 +14379,11 @@
         <v>6874</v>
       </c>
       <c t="s" r="C412" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14330,13 +14392,13 @@
         <v>118</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14350,23 +14412,23 @@
         <v>6875</v>
       </c>
       <c t="s" r="C413" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>118</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>72</v>
@@ -14402,7 +14464,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14411,10 +14473,10 @@
         <v>118</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>125</v>
@@ -14435,22 +14497,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>118</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14483,7 +14545,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14495,17 +14557,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>75</v>
       </c>
       <c t="s" r="K418" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14520,7 +14582,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14529,20 +14591,20 @@
         <v>27</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>141</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>176</v>
+        <v>300</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14557,29 +14619,29 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>71</v>
+        <v>448</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14594,29 +14656,29 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>139</v>
       </c>
       <c t="s" r="K421" s="7">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>194</v>
+        <v>245</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14642,11 +14704,11 @@
         <v>340</v>
       </c>
       <c t="s" r="C423" s="7">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14658,15 +14720,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14681,7 +14743,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14690,17 +14752,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c t="s" r="I424" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
+      <c t="s" r="M424" s="7">
+        <v>301</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
@@ -14714,13 +14778,13 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>17</v>
@@ -14729,7 +14793,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14762,7 +14826,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14771,13 +14835,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14785,7 +14849,7 @@
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c t="s" r="A428" s="9">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
@@ -14805,7 +14869,7 @@
     <row r="429" ht="65.25" customHeight="1"/>
     <row r="430" ht="17.25" customHeight="1">
       <c t="s" r="A430" s="10">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B430" s="10"/>
       <c r="C430" s="10"/>
@@ -14818,7 +14882,7 @@
       <c r="J430" s="10"/>
       <c r="K430" s="10"/>
       <c t="s" r="L430" s="11">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M430" s="11"/>
       <c r="N430" s="11"/>
